--- a/VR_Interactions_Ko.xlsx
+++ b/VR_Interactions_Ko.xlsx
@@ -15315,7 +15315,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82807794-1EE9-46DE-8DDE-903D0A149361}">
-  <dimension ref="A14:AH102"/>
+  <dimension ref="A14:AH103"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -17308,6 +17308,100 @@
         <v>6</v>
       </c>
     </row>
+    <row r="34" spans="1:34">
+      <c r="A34" s="21"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8">
+        <v>20</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="8">
+        <v>22</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="15">
+        <v>6</v>
+      </c>
+      <c r="J34" s="15">
+        <v>5</v>
+      </c>
+      <c r="K34" s="15">
+        <v>5</v>
+      </c>
+      <c r="L34" s="15">
+        <v>2</v>
+      </c>
+      <c r="M34" s="15">
+        <v>3</v>
+      </c>
+      <c r="N34" s="15">
+        <v>4</v>
+      </c>
+      <c r="O34" s="15">
+        <v>5</v>
+      </c>
+      <c r="P34" s="15">
+        <v>6</v>
+      </c>
+      <c r="Q34" s="15">
+        <v>2</v>
+      </c>
+      <c r="R34" s="15">
+        <v>5</v>
+      </c>
+      <c r="S34" s="15">
+        <v>3</v>
+      </c>
+      <c r="T34" s="15">
+        <v>3</v>
+      </c>
+      <c r="U34" s="15">
+        <v>5</v>
+      </c>
+      <c r="V34" s="15">
+        <v>5</v>
+      </c>
+      <c r="W34" s="15">
+        <v>3</v>
+      </c>
+      <c r="X34" s="15">
+        <v>4</v>
+      </c>
+      <c r="Y34" s="15">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="15">
+        <v>4</v>
+      </c>
+      <c r="AA34" s="15">
+        <v>3</v>
+      </c>
+      <c r="AB34" s="15">
+        <v>6</v>
+      </c>
+      <c r="AC34" s="15">
+        <v>3</v>
+      </c>
+      <c r="AD34" s="15">
+        <v>6</v>
+      </c>
+      <c r="AE34" s="15">
+        <v>2</v>
+      </c>
+      <c r="AF34" s="15">
+        <v>3</v>
+      </c>
+      <c r="AG34" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH34" s="15">
+        <v>4</v>
+      </c>
+    </row>
     <row r="37" spans="1:34">
       <c r="A37" s="18"/>
       <c r="B37" s="5"/>
@@ -19148,6 +19242,98 @@
         <v>5</v>
       </c>
     </row>
+    <row r="57" spans="1:34">
+      <c r="A57" s="21"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8">
+        <v>20</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" s="8">
+        <v>22</v>
+      </c>
+      <c r="F57" s="8"/>
+      <c r="I57" s="15">
+        <v>3</v>
+      </c>
+      <c r="J57" s="15">
+        <v>6</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5</v>
+      </c>
+      <c r="L57" s="15">
+        <v>3</v>
+      </c>
+      <c r="M57" s="15">
+        <v>4</v>
+      </c>
+      <c r="N57" s="15">
+        <v>3</v>
+      </c>
+      <c r="O57" s="15">
+        <v>3</v>
+      </c>
+      <c r="P57" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="15">
+        <v>3</v>
+      </c>
+      <c r="R57" s="15">
+        <v>5</v>
+      </c>
+      <c r="S57" s="15">
+        <v>5</v>
+      </c>
+      <c r="T57" s="15">
+        <v>4</v>
+      </c>
+      <c r="U57" s="15">
+        <v>5</v>
+      </c>
+      <c r="V57" s="15">
+        <v>3</v>
+      </c>
+      <c r="W57" s="15">
+        <v>3</v>
+      </c>
+      <c r="X57" s="15">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="15">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="15">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH57" s="15">
+        <v>4</v>
+      </c>
+    </row>
     <row r="60" spans="1:34">
       <c r="A60" s="18"/>
       <c r="B60" s="5"/>
@@ -20988,6 +21174,98 @@
         <v>7</v>
       </c>
     </row>
+    <row r="80" spans="1:34">
+      <c r="A80" s="21"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8">
+        <v>20</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="8">
+        <v>22</v>
+      </c>
+      <c r="F80" s="8"/>
+      <c r="I80" s="15">
+        <v>5</v>
+      </c>
+      <c r="J80" s="15">
+        <v>5</v>
+      </c>
+      <c r="K80" s="15">
+        <v>3</v>
+      </c>
+      <c r="L80" s="15">
+        <v>3</v>
+      </c>
+      <c r="M80" s="15">
+        <v>3</v>
+      </c>
+      <c r="N80" s="15">
+        <v>5</v>
+      </c>
+      <c r="O80" s="15">
+        <v>5</v>
+      </c>
+      <c r="P80" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q80" s="15">
+        <v>4</v>
+      </c>
+      <c r="R80" s="15">
+        <v>3</v>
+      </c>
+      <c r="S80" s="15">
+        <v>5</v>
+      </c>
+      <c r="T80" s="15">
+        <v>5</v>
+      </c>
+      <c r="U80" s="15">
+        <v>6</v>
+      </c>
+      <c r="V80" s="15">
+        <v>4</v>
+      </c>
+      <c r="W80" s="15">
+        <v>5</v>
+      </c>
+      <c r="X80" s="15">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="15">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AA80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB80" s="15">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD80" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AF80" s="15">
+        <v>3</v>
+      </c>
+      <c r="AG80" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH80" s="15">
+        <v>5</v>
+      </c>
+    </row>
     <row r="83" spans="1:34">
       <c r="A83" s="18"/>
       <c r="B83" s="5"/>
@@ -22826,6 +23104,98 @@
       </c>
       <c r="AH102" s="17">
         <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:34">
+      <c r="A103" s="21"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8">
+        <v>20</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" s="8">
+        <v>22</v>
+      </c>
+      <c r="F103" s="8"/>
+      <c r="I103" s="15">
+        <v>6</v>
+      </c>
+      <c r="J103" s="15">
+        <v>6</v>
+      </c>
+      <c r="K103" s="15">
+        <v>2</v>
+      </c>
+      <c r="L103" s="15">
+        <v>3</v>
+      </c>
+      <c r="M103" s="15">
+        <v>3</v>
+      </c>
+      <c r="N103" s="15">
+        <v>5</v>
+      </c>
+      <c r="O103" s="15">
+        <v>5</v>
+      </c>
+      <c r="P103" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="15">
+        <v>4</v>
+      </c>
+      <c r="R103" s="15">
+        <v>2</v>
+      </c>
+      <c r="S103" s="15">
+        <v>5</v>
+      </c>
+      <c r="T103" s="15">
+        <v>4</v>
+      </c>
+      <c r="U103" s="15">
+        <v>3</v>
+      </c>
+      <c r="V103" s="15">
+        <v>5</v>
+      </c>
+      <c r="W103" s="15">
+        <v>5</v>
+      </c>
+      <c r="X103" s="15">
+        <v>5</v>
+      </c>
+      <c r="Y103" s="15">
+        <v>4</v>
+      </c>
+      <c r="Z103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AB103" s="15">
+        <v>5</v>
+      </c>
+      <c r="AC103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AD103" s="15">
+        <v>5</v>
+      </c>
+      <c r="AE103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AF103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AG103" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH103" s="17">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/VR_Interactions_Ko.xlsx
+++ b/VR_Interactions_Ko.xlsx
@@ -8781,6 +8781,9 @@
       <c r="U9">
         <v>4</v>
       </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:71">
       <c r="A10" s="37"/>
@@ -8844,6 +8847,9 @@
       <c r="U10">
         <v>4</v>
       </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:71" ht="13.5">
       <c r="A11" s="40" t="s">
@@ -8908,6 +8914,9 @@
       </c>
       <c r="U11">
         <v>4</v>
+      </c>
+      <c r="V11">
+        <v>3</v>
       </c>
       <c r="BS11" s="22" t="s">
         <v>43</v>
@@ -8975,6 +8984,9 @@
       <c r="U12">
         <v>4</v>
       </c>
+      <c r="V12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:71">
       <c r="A13" s="40" t="s">
@@ -9039,6 +9051,9 @@
       </c>
       <c r="U13">
         <v>4</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:71">
@@ -9103,6 +9118,9 @@
       <c r="U14">
         <v>4</v>
       </c>
+      <c r="V14">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:71" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:71" ht="20.25">
@@ -9110,7 +9128,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="12.75" customHeight="1">
+    <row r="17" spans="1:22" ht="12.75" customHeight="1">
       <c r="A17" s="36" t="s">
         <v>82</v>
       </c>
@@ -9174,8 +9192,11 @@
       <c r="U17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="12.75" customHeight="1">
       <c r="A18" s="37"/>
       <c r="B18" t="s">
         <v>7</v>
@@ -9237,8 +9258,11 @@
       <c r="U18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="40" t="s">
         <v>77</v>
       </c>
@@ -9302,8 +9326,11 @@
       <c r="U19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="37"/>
       <c r="B20" t="s">
         <v>9</v>
@@ -9365,8 +9392,11 @@
       <c r="U20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="40" t="s">
         <v>78</v>
       </c>
@@ -9430,8 +9460,11 @@
       <c r="U21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="37"/>
       <c r="B22" t="s">
         <v>11</v>
@@ -9492,6 +9525,9 @@
       </c>
       <c r="U22">
         <v>3</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="12.75" customHeight="1"/>
@@ -9500,7 +9536,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="12.75" customHeight="1">
+    <row r="25" spans="1:22" ht="12.75" customHeight="1">
       <c r="A25" s="40" t="s">
         <v>76</v>
       </c>
@@ -9564,8 +9600,11 @@
       <c r="U25" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V25" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="12.75" customHeight="1">
       <c r="A26" s="37"/>
       <c r="B26" s="5" t="s">
         <v>7</v>
@@ -9627,8 +9666,11 @@
       <c r="U26" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="40" t="s">
         <v>77</v>
       </c>
@@ -9692,8 +9734,11 @@
       <c r="U27" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="37"/>
       <c r="B28" s="5" t="s">
         <v>9</v>
@@ -9755,8 +9800,11 @@
       <c r="U28" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="40" t="s">
         <v>78</v>
       </c>
@@ -9820,8 +9868,11 @@
       <c r="U29" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="37"/>
       <c r="B30" s="5" t="s">
         <v>11</v>
@@ -9883,13 +9934,16 @@
       <c r="U30" s="8">
         <v>3</v>
       </c>
+      <c r="V30" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:21" ht="20.25">
       <c r="A32" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:22">
       <c r="A33" s="40" t="s">
         <v>76</v>
       </c>
@@ -9953,8 +10007,11 @@
       <c r="U33" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V33" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="12.75" customHeight="1">
       <c r="A34" s="37"/>
       <c r="B34" s="5" t="s">
         <v>7</v>
@@ -10016,8 +10073,11 @@
       <c r="U34" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="V34" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="40" t="s">
         <v>77</v>
       </c>
@@ -10081,8 +10141,11 @@
       <c r="U35" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="V35" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="37"/>
       <c r="B36" s="5" t="s">
         <v>9</v>
@@ -10144,8 +10207,11 @@
       <c r="U36" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V36" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="12.75" customHeight="1">
       <c r="A37" s="40" t="s">
         <v>78</v>
       </c>
@@ -10209,8 +10275,11 @@
       <c r="U37" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V37" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="12.75" customHeight="1">
       <c r="A38" s="37"/>
       <c r="B38" s="5" t="s">
         <v>11</v>
@@ -10271,6 +10340,9 @@
       </c>
       <c r="U38" s="8">
         <v>2</v>
+      </c>
+      <c r="V38" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="12.75" customHeight="1"/>
@@ -10281,7 +10353,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="18">
+    <row r="45" spans="1:22" ht="18">
       <c r="A45" s="25" t="s">
         <v>72</v>
       </c>
@@ -10345,8 +10417,11 @@
       <c r="U45" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="V45" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" s="40" t="s">
         <v>73</v>
       </c>
@@ -10410,8 +10485,11 @@
       <c r="U46" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="V46" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" s="37"/>
       <c r="B47" s="24" t="s">
         <v>14</v>
@@ -10473,8 +10551,11 @@
       <c r="U47" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="V47" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" s="40" t="s">
         <v>74</v>
       </c>
@@ -10538,8 +10619,11 @@
       <c r="U48" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="41"/>
       <c r="B49" s="24" t="s">
         <v>16</v>
@@ -10601,8 +10685,11 @@
       <c r="U49" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="V49" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" s="37"/>
       <c r="B50" s="24" t="s">
         <v>17</v>
@@ -10664,8 +10751,11 @@
       <c r="U50" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="51" spans="1:21">
+      <c r="V50" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="40" t="s">
         <v>75</v>
       </c>
@@ -10729,8 +10819,11 @@
       <c r="U51" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="52" spans="1:21">
+      <c r="V51" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
       <c r="A52" s="37"/>
       <c r="B52" s="24" t="s">
         <v>19</v>
@@ -10791,6 +10884,9 @@
       </c>
       <c r="U52" s="8" t="s">
         <v>36</v>
+      </c>
+      <c r="V52" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -11764,6 +11860,9 @@
       <c r="U9" s="4">
         <v>2</v>
       </c>
+      <c r="V9" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:71">
       <c r="A10" s="37"/>
@@ -11827,6 +11926,9 @@
       <c r="U10" s="4">
         <v>4</v>
       </c>
+      <c r="V10" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:71" ht="13.5">
       <c r="A11" s="40" t="s">
@@ -11891,6 +11993,9 @@
       </c>
       <c r="U11" s="4">
         <v>2</v>
+      </c>
+      <c r="V11" s="4">
+        <v>5</v>
       </c>
       <c r="BS11" s="22" t="s">
         <v>43</v>
@@ -11958,6 +12063,9 @@
       <c r="U12" s="4">
         <v>4</v>
       </c>
+      <c r="V12" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:71">
       <c r="A13" s="40" t="s">
@@ -12022,6 +12130,9 @@
       </c>
       <c r="U13" s="4">
         <v>5</v>
+      </c>
+      <c r="V13" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:71">
@@ -12086,6 +12197,9 @@
       <c r="U14" s="4">
         <v>5</v>
       </c>
+      <c r="V14" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:71" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:71" ht="18">
@@ -12093,7 +12207,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="12.75" customHeight="1">
+    <row r="17" spans="1:22" ht="12.75" customHeight="1">
       <c r="A17" s="40" t="s">
         <v>76</v>
       </c>
@@ -12157,8 +12271,11 @@
       <c r="U17" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V17" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="12.75" customHeight="1">
       <c r="A18" s="37"/>
       <c r="B18" s="5" t="s">
         <v>7</v>
@@ -12220,8 +12337,11 @@
       <c r="U18" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="40" t="s">
         <v>77</v>
       </c>
@@ -12285,8 +12405,11 @@
       <c r="U19" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="37"/>
       <c r="B20" s="5" t="s">
         <v>9</v>
@@ -12348,8 +12471,11 @@
       <c r="U20" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="40" t="s">
         <v>78</v>
       </c>
@@ -12413,8 +12539,11 @@
       <c r="U21" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="37"/>
       <c r="B22" s="5" t="s">
         <v>11</v>
@@ -12474,6 +12603,9 @@
         <v>3</v>
       </c>
       <c r="U22" s="8">
+        <v>2</v>
+      </c>
+      <c r="V22" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12483,7 +12615,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="12.75" customHeight="1">
+    <row r="25" spans="1:22" ht="12.75" customHeight="1">
       <c r="A25" s="40" t="s">
         <v>76</v>
       </c>
@@ -12547,8 +12679,11 @@
       <c r="U25" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V25" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="12.75" customHeight="1">
       <c r="A26" s="37"/>
       <c r="B26" s="5" t="s">
         <v>7</v>
@@ -12610,8 +12745,11 @@
       <c r="U26" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="40" t="s">
         <v>77</v>
       </c>
@@ -12675,8 +12813,11 @@
       <c r="U27" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="37"/>
       <c r="B28" s="5" t="s">
         <v>9</v>
@@ -12738,8 +12879,11 @@
       <c r="U28" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="40" t="s">
         <v>78</v>
       </c>
@@ -12803,8 +12947,11 @@
       <c r="U29" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="37"/>
       <c r="B30" s="5" t="s">
         <v>11</v>
@@ -12865,6 +13012,9 @@
       </c>
       <c r="U30" s="8">
         <v>3</v>
+      </c>
+      <c r="V30" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="12.75" customHeight="1"/>
@@ -12878,7 +13028,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="18">
+    <row r="45" spans="1:22" ht="18">
       <c r="A45" s="25" t="s">
         <v>72</v>
       </c>
@@ -12942,8 +13092,11 @@
       <c r="U45" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="V45" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" s="40" t="s">
         <v>73</v>
       </c>
@@ -13007,8 +13160,11 @@
       <c r="U46" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="V46" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" s="37"/>
       <c r="B47" s="27" t="s">
         <v>22</v>
@@ -13070,8 +13226,11 @@
       <c r="U47" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="V47" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" s="40" t="s">
         <v>74</v>
       </c>
@@ -13135,8 +13294,11 @@
       <c r="U48" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="37"/>
       <c r="B49" s="27" t="s">
         <v>24</v>
@@ -13198,8 +13360,11 @@
       <c r="U49" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="V49" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" s="40" t="s">
         <v>75</v>
       </c>
@@ -13263,8 +13428,11 @@
       <c r="U50" s="15" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="51" spans="1:21">
+      <c r="V50" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="37"/>
       <c r="B51" s="28" t="s">
         <v>26</v>
@@ -13324,6 +13492,9 @@
         <v>34</v>
       </c>
       <c r="U51" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="V51" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -13470,6 +13641,9 @@
       <c r="U9" s="12">
         <v>4</v>
       </c>
+      <c r="V9" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" s="42"/>
@@ -13533,6 +13707,9 @@
       <c r="U10" s="12">
         <v>4</v>
       </c>
+      <c r="V10" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" s="42" t="s">
@@ -13597,6 +13774,9 @@
       </c>
       <c r="U11" s="12">
         <v>3</v>
+      </c>
+      <c r="V11" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -13661,6 +13841,9 @@
       <c r="U12" s="12">
         <v>4</v>
       </c>
+      <c r="V12" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" s="42" t="s">
@@ -13724,6 +13907,9 @@
         <v>4</v>
       </c>
       <c r="U13" s="12">
+        <v>4</v>
+      </c>
+      <c r="V13" s="12">
         <v>4</v>
       </c>
     </row>
@@ -13789,6 +13975,9 @@
       <c r="U14" s="12">
         <v>4</v>
       </c>
+      <c r="V14" s="12">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:60" ht="13.5">
       <c r="BH15" s="22" t="s">
@@ -13800,7 +13989,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:22">
       <c r="A17" s="42" t="s">
         <v>76</v>
       </c>
@@ -13864,8 +14053,11 @@
       <c r="U17" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="42"/>
       <c r="B18" s="13" t="s">
         <v>7</v>
@@ -13927,8 +14119,11 @@
       <c r="U18" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="42" t="s">
         <v>77</v>
       </c>
@@ -13992,8 +14187,11 @@
       <c r="U19" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="42"/>
       <c r="B20" s="13" t="s">
         <v>9</v>
@@ -14055,8 +14253,11 @@
       <c r="U20" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="42" t="s">
         <v>78</v>
       </c>
@@ -14120,8 +14321,11 @@
       <c r="U21" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="42"/>
       <c r="B22" s="13" t="s">
         <v>11</v>
@@ -14183,13 +14387,16 @@
       <c r="U22" s="15">
         <v>2</v>
       </c>
+      <c r="V22" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:21" ht="18">
       <c r="A24" s="32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:22">
       <c r="A25" s="42" t="s">
         <v>76</v>
       </c>
@@ -14253,8 +14460,11 @@
       <c r="U25" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:21">
+      <c r="V25" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="42"/>
       <c r="B26" s="13" t="s">
         <v>7</v>
@@ -14316,8 +14526,11 @@
       <c r="U26" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="42" t="s">
         <v>77</v>
       </c>
@@ -14381,8 +14594,11 @@
       <c r="U27" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="42"/>
       <c r="B28" s="13" t="s">
         <v>9</v>
@@ -14444,8 +14660,11 @@
       <c r="U28" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="42" t="s">
         <v>78</v>
       </c>
@@ -14509,8 +14728,11 @@
       <c r="U29" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="42"/>
       <c r="B30" s="13" t="s">
         <v>11</v>
@@ -14572,13 +14794,16 @@
       <c r="U30" s="15">
         <v>3</v>
       </c>
+      <c r="V30" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:21" ht="18">
       <c r="A32" s="32" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:22">
       <c r="A33" s="42" t="s">
         <v>76</v>
       </c>
@@ -14642,8 +14867,11 @@
       <c r="U33" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:21">
+      <c r="V33" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="42"/>
       <c r="B34" s="13" t="s">
         <v>7</v>
@@ -14705,8 +14933,11 @@
       <c r="U34" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="V34" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="42" t="s">
         <v>77</v>
       </c>
@@ -14770,8 +15001,11 @@
       <c r="U35" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="V35" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="42"/>
       <c r="B36" s="13" t="s">
         <v>9</v>
@@ -14833,8 +15067,11 @@
       <c r="U36" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:21">
+      <c r="V36" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" s="42" t="s">
         <v>78</v>
       </c>
@@ -14898,8 +15135,11 @@
       <c r="U37" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:21">
+      <c r="V37" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" s="42"/>
       <c r="B38" s="13" t="s">
         <v>11</v>
@@ -14961,13 +15201,16 @@
       <c r="U38" s="15">
         <v>2</v>
       </c>
+      <c r="V38" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:21" ht="20.25">
       <c r="A44" s="35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="20.25">
+    <row r="45" spans="1:22" ht="20.25">
       <c r="A45" s="30" t="s">
         <v>71</v>
       </c>
@@ -15031,8 +15274,11 @@
       <c r="U45" s="15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" ht="20.25">
+      <c r="V45" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="20.25">
       <c r="A46" s="29" t="s">
         <v>81</v>
       </c>
@@ -15096,8 +15342,11 @@
       <c r="U46" s="15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" ht="18">
+      <c r="V46" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="18">
       <c r="A47" s="25" t="s">
         <v>79</v>
       </c>
@@ -15161,8 +15410,11 @@
       <c r="U47" s="15" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="V47" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" s="42" t="s">
         <v>80</v>
       </c>
@@ -15226,8 +15478,11 @@
       <c r="U48" s="15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="42"/>
       <c r="B49" s="28" t="s">
         <v>31</v>
@@ -15288,6 +15543,9 @@
       </c>
       <c r="U49" s="15" t="s">
         <v>35</v>
+      </c>
+      <c r="V49" s="15" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -17309,8 +17567,12 @@
       </c>
     </row>
     <row r="34" spans="1:34">
-      <c r="A34" s="21"/>
-      <c r="B34" s="8"/>
+      <c r="A34" s="21">
+        <v>45838.7572337963</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="C34" s="8">
         <v>20</v>
       </c>
